--- a/data/processed/JRGsamples/JRG40.xlsx
+++ b/data/processed/JRGsamples/JRG40.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinby/Desktop/AI44PT_Desktop/data/processed/JRGsamples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9F23F1-9A01-D84C-AF86-16B4FE1210C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BFC970-FED8-4443-8DD9-97600646620E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{1C61E315-60CB-454A-BC54-24BB21AF3D08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -220,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="537">
   <si>
     <t>#</t>
   </si>
@@ -252,10 +252,46 @@
     <t>Intercoder reliability</t>
   </si>
   <si>
+    <t>doi:10.1111/rego.12192</t>
+  </si>
+  <si>
+    <t>Understanding voluntary program performance: Introducing the diffusion network perspective</t>
+  </si>
+  <si>
+    <t>Jeroen van der Heijden</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
+    <t>Interaction of program design conditions in affecting performance of voluntary programs</t>
+  </si>
+  <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Geographical focus in several countries with no clearly specified on the ground problem</t>
+  </si>
+  <si>
+    <t>Looks at the topic of low carbon building and city development across cases in Australia, the Netherlands and the US</t>
+  </si>
+  <si>
+    <t>Explores implications on voluntary program performance of the diffusion network</t>
+  </si>
+  <si>
+    <t>This article has introduced the diffusion network perspective as a critical condition to understand voluntary program performance.</t>
+  </si>
+  <si>
+    <t>Key objective: determinants of voluntary program performance, which originates from high cost of direct regulatory intervention</t>
+  </si>
+  <si>
+    <t>Voluntary programs aim to change the behavior of individuals and organizations, but without the force of law. They have rapidly become popular governance instruments in situations in which it is too costly or difficult to implement direct regulatory interventions, for instance because of political unwillingness (Darnall &amp; Carmin 2005). They also provide an opportunity to showcase and market desired “beyond compliance” behavior, or to reward leading firms (Saurwein 2011).</t>
+  </si>
+  <si>
+    <t>Looks at how diffusion network perspective can relate to better voluntary program results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The diffusion network perspective, as conceptualized in this article, brings together these insights and argues that the stronger the diffusion network, the more likely it is that a voluntary program will achieve the desired results. </t>
   </si>
   <si>
     <t>Type 2</t>
@@ -271,6 +307,41 @@
 Beatrice</t>
   </si>
   <si>
+    <t>doi:10.1111/rego.12185</t>
+  </si>
+  <si>
+    <t>Community structure and the behavior of transnational sustainability governors: Toward a multi-relational approach</t>
+  </si>
+  <si>
+    <t>Luc Fransen
+Jelmer Schalk
+Graeme Auld</t>
+  </si>
+  <si>
+    <t>How community structures of transnational private governance organizations (TPGOs) influence TPGO behaviour</t>
+  </si>
+  <si>
+    <t>Focus on agricultural TPGOs with diverse features and across diverse geography</t>
+  </si>
+  <si>
+    <t>Our empirical case is the agriculture sector where we examine 16 TPGOs that advance overlapping attention to sustainability. Following recent literature and policy vocabulary (Bitzer et al. 2012; Marx &amp; Wouters 2014), we understand sustainability-focused TPGOs to promote economic, and/or social, and/or environmental criteria for production. Agriculture is a useful sector for study because of the signiﬁcant sustainable development challenges faced. Moreover, the overall density of agriculture TPGOs facilitates an exploration of different community structures and their potential consequences for TPGO behavior.</t>
+  </si>
+  <si>
+    <t>Implication on global sustainability governance and findings for policymakers</t>
+  </si>
+  <si>
+    <t>Our theoretical discussion of the different ties among TPGOs and their implications for community structure signals how communities are built out of a variety of ties, and how different degrees of community formation may be at play, with different effects on policy and policy outcomes. This approach to studying interactions may therefore contribute to our understanding of how global sustainability governance evolves, and the degree to which ties and communities shape and possibly change the evolutionary trajectory of policymakers.</t>
+  </si>
+  <si>
+    <t>TPGO focus does not involve utility maximisation</t>
+  </si>
+  <si>
+    <t>Transnational private governance organizations (TPGOs) set standards, procedures, and governance models for various sustainability issues and global industries.</t>
+  </si>
+  <si>
+    <t>TPGO focus</t>
+  </si>
+  <si>
     <t>Type 3</t>
   </si>
   <si>
@@ -284,6 +355,87 @@
   </si>
   <si>
     <t>Match</t>
+  </si>
+  <si>
+    <t>doi:10.1111/rego.12182</t>
+  </si>
+  <si>
+    <t>Promoting customer engagement: A new trend in utility regulation</t>
+  </si>
+  <si>
+    <t>Robert Hahn
+Robert Metcalfe
+Florian Rundhammer</t>
+  </si>
+  <si>
+    <t>Customer engagement (CE) in utilities regulation</t>
+  </si>
+  <si>
+    <t>Theories about CE generated across diff env topics, energy and water regulation</t>
+  </si>
+  <si>
+    <t>Third, we develop two detailed case studies of an energy regulator and a water regulator in the United Kingdom (UK) at the forefront of CE efforts: the Ofﬁce for Gas and Electricity Markets (Ofgem) and the Ofﬁce for Water Services Regulation Authority (Ofwat). 3 In both cases, regulators and stakeholders are generally satisﬁed with the outcomes of CE. Regulated ﬁrms appear to have increased their engagement efforts after the regulators explicitly incorporated CE in their price reviews. We ﬁnd, however, that incentives for ﬁrms to engage with their customers, and to use particular tools in the process, are not clearly speciﬁed. There does not appear to be a direct link between the engagement strategy used and the economic incentives received by a ﬁrm.</t>
+  </si>
+  <si>
+    <t>Conclusion implications centres around broad scope of utility regulation</t>
+  </si>
+  <si>
+    <t>We also suggested that more careful program evaluation should become a central part of utility regulation</t>
+  </si>
+  <si>
+    <t>Apt for an article on utilities to focus on utility…. Analysis centres around improving economic effiiciency</t>
+  </si>
+  <si>
+    <t>We then examined the effectiveness of CE and were unable to ﬁnd rigorous studies that document a clear relationship between CE and economic variables of interest. We conjecture that this result arises because of the analytical problems in demonstrating effectiveness, particularly related to specifying a believable counterfactual in the complex world of utility regulation.</t>
+  </si>
+  <si>
+    <t>Implications centre around economic effciency</t>
+  </si>
+  <si>
+    <t>Finally, we explored how to improve the process of CE. We suggested that introducing economic efﬁciency explicitly as a yardstick for evaluating CE could be helpful. We further argued that clearer and more direct incentives for CE could be helpful in motivating regulated ﬁrms and customer groups.</t>
+  </si>
+  <si>
+    <t>5 - Very Hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type 2
+as the article seems to generate universal theories about CE across different environmental topics, specifically using both energy and water regulators as case study. Focuses more on governance and regulation rather than the the actual outcomes/effects to the environment </t>
+  </si>
+  <si>
+    <t>doi:10.1111/rego.12212</t>
+  </si>
+  <si>
+    <t>Assessing the institutionalization of private sustainability governance in a changing coffee sector</t>
+  </si>
+  <si>
+    <t>Janina Grabs</t>
+  </si>
+  <si>
+    <t>Investigating transnational private governance initiatives in the coffee sector</t>
+  </si>
+  <si>
+    <t>Coffee industry was selected owing to its established experience of private governance</t>
+  </si>
+  <si>
+    <t>This study examines whether such institutionalization has occurred in the coffee sector, the commodity with the most widespread adoption of certiﬁed products and over 30 years’ experience of private governance, and tests hypotheses on facilitating and inhibiting conditions. The coffee industry, where private sustainability certiﬁcation and veriﬁcation schemes have existed for over 30 years and cover almost half of the world’s production volume, provides a powerful case study to explore whether, how, and why institutionalization at the global level may (not) be occurring, and to test theoretical assumptions to that effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Findings aimed to be generalisable on private instutionalisation </t>
+  </si>
+  <si>
+    <t>I primarily focus here on whether institutionalization occurs at the global level of industry</t>
+  </si>
+  <si>
+    <t>While article acknowledges the origins of coffee certification as profit maximising, the focus of the article stands on the institutionalisation of private governance for sustainability (non-utility)</t>
+  </si>
+  <si>
+    <t>The coffee industry, where private sustainability certiﬁcation and veriﬁcation schemes have existed for over 30 years and cover almost half of the world’s production volume, provides a powerful case study to explore whether, how, and why institutionalization at the global level may (not) be occurring, and to test theoretical assumptions to that effect.</t>
+  </si>
+  <si>
+    <t>Concludes with implications on the state of instutitonalisation in private sustainability governance</t>
+  </si>
+  <si>
+    <t>The analysis has furthermore shown that conclusions on the state of the institutionalization of private sustainability governance are highly dependent on the speciﬁc deﬁnition – and relatedly, the dependent variable – used. Furthermore, as Table 4 shows, different forms of institutionalization will have varying facilitating or inhibiting conditions that might stand in direct conﬂict with each other.</t>
   </si>
   <si>
     <t>2 - Easy</t>
@@ -294,22 +446,271 @@
 Bo</t>
   </si>
   <si>
+    <t>doi:10.1111/rego.12213</t>
+  </si>
+  <si>
+    <t>Business interests in salmon aquaculture certification: Competition or collective action?</t>
+  </si>
+  <si>
+    <t>Irja Vormedal
+Lars H. Gulbrandsen</t>
+  </si>
+  <si>
     <t>Lars H. Gulbrandsen</t>
   </si>
   <si>
+    <t>Addressing problems of social and environmental concern through transnational private governance initiatives</t>
+  </si>
+  <si>
+    <t>Salmon Aquaculture Case Study  is used to derive findings towards a class of problems - managing common pooled resources</t>
+  </si>
+  <si>
+    <t>This article examines a range of competition and collective action-related interests that can motivate ﬁrms to promote and adopt certiﬁcation schemes. We pay particular attention to the hitherto underexplored collective action interest to safeguard common-pool resources, upon which an industry may depend to sustain yields. Based on a case study of salmon aquaculture certiﬁcation, the article argues that while the corporate motives repertoire includes strengthening competitiveness and industry reputation, safeguarding shared waters for culturing salmon is key to explaining industry commitment to and adoption of private regulation in this sector.</t>
+  </si>
+  <si>
+    <t>specifically looks at competition and collective action interests that motivate firms to manage common pooled resources. Seems to limit findings to managing CPRs using certification programs</t>
+  </si>
+  <si>
+    <t>More generally, our study conﬁrms the importance of many strategic business motives identiﬁed in the literature on non-state sustainability certiﬁcation, such as the aim to strengthen ﬁrm competitiveness and reap ﬁrstmover advantages through differentiation and focus on eco-market segments (competition) and improving the industry’s reputation (collective action). But our study also demonstrates the importance of the understudied collective action interest to manage common-pool resources, to enable long-term industry survival and future growth. The centrality of this interest in explaining why key business actors have committed to and adopted aquaculture certiﬁcation provides support for a functionalist understanding of the emergence and growth of private authority, grounded in the literature on liberal institutionalism.</t>
+  </si>
+  <si>
+    <t>Analysis focuses on economic optimisation - as the driver behind uptake of private governance certification schemes</t>
+  </si>
+  <si>
+    <t>In sum, we argue that collective action-based motives, in particular to protect or improve the reputation of a group of companies (or an entire industry), and/or to safeguard a common-pool resource upon which an industry may depend, represent two potentially important drivers behind company uptake of certiﬁcation schemes. We examine both motives in our empirical investigation of aquaculture certiﬁcation but pay particular attention to the motive to manage common-pool resources through certiﬁcation.</t>
+  </si>
+  <si>
+    <t>Concludes that primary driver of motivation is utility</t>
+  </si>
+  <si>
+    <t>The multinational companies stressed the importance of their self-interest to achieve “biological control,” and thus the motive to scale up the regulation and governance of biological contamination. Because the industry operates in a common – sharing public waters for culturing salmon – elevated levels of parasites, virus, and bacteria in one farm can spread fast via currents and contaminate the larger water area, causing widespread ﬁsh disease, high mortality rates, stock reduction, and in the extreme, fallowing. Therefore, the Norwegian multinationals have become advocates of stricter production standards, and particularly in regions such as Chile, where public regulations are considered inadequate for dealing with biological risks. Through broad implementation of the ASC certiﬁcation program, the multinationals believe industry actors can improve their control over parasite and ﬁsh disease transmission, and therefore also the ability to sustain farmed salmon yields. For Marine Harvest – a giant that manages 233 of the 1,051 Norwegian licenses 8 and operates in nearly all Norwegian production regions – the motive to enhance biological control in shared waters also applies to Norway, probably because of their high exposure to neighboring companies. This supports our hypothesis that certiﬁcation, as a particularly rigorous form of private regulation, can be utilized strategically by business actors to deal effectively with commonpool resource challenges that pose a risk to their business operations.</t>
+  </si>
+  <si>
     <t>Type 1</t>
   </si>
   <si>
+    <t>I may have coded this as Type 1. 
+Seems like they are generating theories about the role of business interests in certification/NSMD regulations. Specifically looks at competition and collective action interests that motivate firms to manage common pooled resources. Seems to limit findings to managing CPRs using certification programs?.</t>
+  </si>
+  <si>
     <t>Non match</t>
   </si>
   <si>
+    <t>doi:10.1111/rego.12172</t>
+  </si>
+  <si>
+    <t>Authoritarian but responsive: Local regulation of industrial energy efficiency in Jiangsu, China</t>
+  </si>
+  <si>
+    <t>Junming Zhu
+Marian R. Chertow</t>
+  </si>
+  <si>
+    <t>Industrial energy efficiency in Jiangsu, China context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focuses on energy targets based on science. Is cognizant of how responsiveness to firm needs can potentially not meet climate chaneg needs. Critiques how pluralism of multiple actors in a decentralized regulatory system can lead to compromise in environmental outcomes. </t>
+  </si>
+  <si>
+    <t>We trace the local implementation and enforcement process in the case of China’s energy efﬁciency policy based on interviews and archival documents from Jiangsu Province. The focus on a single but comprehensive regulatory area helps us build and test our conceptualization model and explanations. As descriptive and explanatory rather than prescriptive, the authoritarian but responsive model we identiﬁed contributes to an understanding of regulatory behaviors and associated impacts within decentralized authoritarian settings. It connects the ideal of responsive regulation with institutional logic and reality in China, showing why and how the government responds and what differences it makes.
+"We trace the local implementation and enforcement process in the case of China’s energy efficiency policy based on interviews and archival documents from Jiangsu Province." "Jiangsu Province has one of the most developed economies and most stringent energy efficiency targets in China."
+"In contrast with considering enforcement as a one-time decision, we focus on the longer-term interactive process between regulators and regulated industrial firms in China, where demands for environmental protection and climate mitigation are an increasingly important dimension of local governments’ administrative concerns."
+"Of course, the dedication to energy efficiency and environmental protection did lead to harsh results, such as closure of hundreds of firms. But with explicit regulatory targets and interactive processes, firms improved their understanding of local regulation and complied and contributed more actively to local govern- ance. All four municipalities improved energy efficiency beyond their own targets without compromising eco- nomic growth."</t>
+  </si>
+  <si>
+    <t>The rationale is embedded in the regionally decentralized authoritarian system in China, where local ofﬁcials are politically responsible to higher authorities for social and economic development, but can apply ﬂexible approaches. On the one hand, local ofﬁcials apply this approach to strengthen and coordinate across different regulatory issues, which improves local governance and ultimately beneﬁts their own careers. On the other hand, responsiveness is restricted in the regulatory process, follows an authoritarian logic, and does not necessarily imply a deliberation and democratization process, or even a decentering of regulation among new political actors. This approach differs from the conceptualization of responsive regulation or responsive authoritarianism in its scale and scope of responsiveness. It also has advantages over the inﬂexible authoritarian environmentalism and highly variable shifts of enforcement styles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Talks a lot about how responsive regulation is the rational choice for local authorities to coordinate across a variety of issues beyond just energy efficiency.  Enforcement of laws were responsive based on how the firm contributed to the community in economic and social angles. Tackles it as a collective action problem. </t>
+  </si>
+  <si>
+    <t>If future policy objectives could be well formulated and linked to local evaluation, enforcement responsiveness might become more likely to be adopted for local optimization over regulatory issues.</t>
+  </si>
+  <si>
+    <t>Analysis focuses on what poses the most rational choice for local governments regarding regulation</t>
+  </si>
+  <si>
+    <t>Embedded in the decentralized authoritarian context, the authoritarian but responsive approach is found to be a rational choice of local governments and different from previous conceptualizations.</t>
+  </si>
+  <si>
+    <t>Cashore
+Beatrice
+Bo
+Ash</t>
+  </si>
+  <si>
+    <t>Type 1
+Focuses on energy targets based on science. Is cognizant of how responsiveness to firm needs can potentially not meet climate chaneg needs. Critiques how pluralism of multiple actors in a decentralized regulatory system can lead to compromise in environmental outcomes. 
+Talks a lot about how responsive regulation is the rational choice for local authorities to coordinate across a variety of issues beyond just energy efficiency.  Enforcement of laws were responsive based on how the firm contributed to the community in economic and social angles. Tackles it as a collective action problem. 
+"We trace the local implementation and enforcement process in the case of China’s energy efficiency policy based on interviews and archival documents from Jiangsu Province." "Jiangsu Province has one of the most developed economies and most stringent energy efficiency targets in China."
+"The need for effective implementation and enforcement of environmental policies is a common issue globally and of particular salience in rapidly industrializing economies."
+"In contrast with considering enforcement as a one-time decision, we focus on the longer-term interactive process between regulators and regulated industrial firms in China, where demands for environmental protection and climate mitigation are an increasingly important dimension of local governments’ administrative concerns."
+"Of course, the dedication to energy efficiency and environmental protection did lead to harsh results, such as closure of hundreds of firms. But with explicit regulatory targets and interactive processes, firms improved their understanding of local regulation and complied and contributed more actively to local govern- ance. All four municipalities improved energy efficiency beyond their own targets without compromising eco- nomic growth."</t>
+  </si>
+  <si>
+    <t>doi:10.1111/rego.12159</t>
+  </si>
+  <si>
+    <t>Transparency in multilateral climate politics: Furthering (or distracting from) accountability?</t>
+  </si>
+  <si>
+    <t>Aarti Gupta
+Harrovan Asselt</t>
+  </si>
+  <si>
+    <t>Transparency and accountability in a multilateral sustainability context</t>
+  </si>
+  <si>
+    <t>Looking at transparency and accountability in a multilateral context</t>
+  </si>
+  <si>
+    <t>This article analyzes the relationship between transparency and accountability in the multilateral climate regime established under the United Nations Framework Convention on Climate Change (UNFCCC).</t>
+  </si>
+  <si>
+    <t>Looks at implications beyond UNFCCC transparency arrangements</t>
+  </si>
+  <si>
+    <t>Another key question is how UNFCCC transparency arrangements might serve to further ex-ante accountability in this context of anticipatory governance, given the transformative changes necessary to achieve the Paris Agreement’s goals. While the global stocktake mandated under the Paris Agreement to be held at ﬁve-yearly intervals from 2023 onwards is intended to play a key role in enhancing (collective) ex-ante accountability, and potentially also collective ambition, its details are yet to be decided. Furthermore, it is unclear how the outcomes of the enhanced transparency framework will feed into the global stocktake,  making this an important issue for further research. How can non-state actors bolster accountability in this multilateral context by serving as intermediaries or leveraging information generated through the formal transparency system (van Asselt 2016)? And how might such efforts feed into the geopolitics of differentiation or the effort to strengthen collective ambition in this multilateral context?</t>
+  </si>
+  <si>
+    <t>Transparency is a type 3 catchword, no utility is involved</t>
+  </si>
+  <si>
+    <t>This article analyzes the interplay between transparency and accountability in multilateral climate politics. The 2015 Paris Agreement calls for a “pledge-and-review” approach to collective climate action with an “enhanced transparency framework” as a key pillar of the Agreement.</t>
+  </si>
+  <si>
+    <t>Conclusion centres around transparency, which involves no utility.</t>
+  </si>
+  <si>
+    <t>We began our analysis by noting that transparency is widely assumed to be essential for securing greater accountability. Our exploratory analysis above points to another proposition with regard to this relationship: that transparency is rather a site mirroring climate accountability conﬂicts.</t>
+  </si>
+  <si>
+    <t>doi:10.1111/rego.12215</t>
+  </si>
+  <si>
+    <t>Between regulatory field structuring and organizational roles: Intermediation in the field of sustainable urban development</t>
+  </si>
+  <si>
+    <t>Joel Bothello
+Afshin Mehrpouya</t>
+  </si>
+  <si>
+    <t>Rule intermediation in the context of an RI, the ICLEI serving as a bridge for sustainable urban development policies between the UN and local authorities</t>
+  </si>
+  <si>
+    <t>Analysis ultimately centres around other Ris</t>
+  </si>
+  <si>
+    <t>In parallel, we sought to situate the role changes vis-à-vis other RIs in the regulatory ﬁeld. The aim was to analyze the tripartite inﬂuences among the focal intermediary, the ﬁeld, and other RIs. A list of the archival sources is provided in Appendix I, totaling approximately 1,300 pages of data.</t>
+  </si>
+  <si>
+    <t>Findings were in relation to other RIs and implications were used to make observations in general about RIs</t>
+  </si>
+  <si>
+    <t>Our case illustrates one possible set of responses by an RI to a regulatory ﬁeld undergoing processes of structuration, as well as how it responds to the concomitant rise of other intermediaries. Our longitudinal analysis of this case aimed to show the contingencies involved, as the structure of a regulatory ﬁeld affects the role of RIs within them. The case of ICLEI is, in other words, a “critical case” (Flyvbjerg 2006), that is, a counterpoint to some work on RIs presenting them as rational and highly agentic actors. The case of ICLEI instead illustrates how the rise or fall of RIs can be conditioned by a constellation of external political shocks, ﬁeld-level events, and actions of regulators, peers, and targets.</t>
+  </si>
+  <si>
+    <t>The general topic of RIs relates to accountability and transparency, type 3 catchwords.</t>
+  </si>
+  <si>
+    <t>In the contemporary era, norms such as competition, democracy, transparency, and environmentalism have come to dominate policymaking and organizational governance (Drori et al. 2006; Mehrpouya &amp; Djelic 2014; Bothello &amp; Salles-Djelic 2017). In this new paradigm, actors, technologies, and knowledge in governance have rapidly proliferated, leading to the rise of regulatory ﬁelds for different public goods (Gulbrandsen 2008; Dingwerth &amp; Pattberg 2009; Fransen 2011; Reinecke et al. 2012). However, the effectiveness of transnational “rules” is contingent upon a constellation of rule-intermediaries (RIs) that not only enable translation, adaptation, and travelling of rules, but also facilitate accountability and push for compliance by the regulatory targets (Levi-Faur &amp; Jordana 2005; Bartley 2007; Djelic 2011b; Abbott et al. 2015).</t>
+  </si>
+  <si>
+    <t>The general topic of RIs relates to accountability and transparency, type 3 catchwords. The conclusion similarly is in relation to Ris</t>
+  </si>
+  <si>
     <t>3 - Medium</t>
   </si>
   <si>
     <t>Cashore</t>
   </si>
   <si>
+    <t xml:space="preserve">Type 3
+focus on regulatory intermediaries as part of a way to understand a highly compex way in which different interests develop policies governing problems (in this case sustainability in cities but no attention to its problem structure per se or what the research means for the problem. not puresly rational choice though
+improving governance Brundlant (totally type 3 even though it refers to tragedies of the commons, too). Counterpart to purely ratioalist accounts. Eventhough it refers to marketization it is simply describing what is happening ratehr than giving it as an explanatory framework....remind me about Babbie </t>
+  </si>
+  <si>
+    <t>doi:10.1111/rego.12241</t>
+  </si>
+  <si>
+    <t>Transparency in transnational governance: The determinants of information disclosure of voluntary sustainability programs</t>
+  </si>
+  <si>
+    <t>Philip Schleifer
+Matteo Fiorini
+Graeme Auld</t>
+  </si>
+  <si>
     <t>Philip Schleifer</t>
+  </si>
+  <si>
+    <t>Transparency in transnational governance</t>
+  </si>
+  <si>
+    <t>Looks at transnational governance across an array of voluntary sustainability programmes</t>
+  </si>
+  <si>
+    <t>Examining the institutional design of 113 voluntary sustainability programs, we ﬁnd a positive correlation between the involvement of public actors and information disclosure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusions centre around transnational governance, transparency relating to it and the doubts raised over accountability </t>
+  </si>
+  <si>
+    <t>The spread of “new” transnational governance has prompted questions about its accountability. Without recourse to principal–agent forms of accountability, scholars and practitioners have proposed transparency as a potential solution. Yet as we have shown, very few studies have documented and explained variation in the practice of transparency in transnational governance. Our analysis contributes to ﬁlling this gap by examining internal and external factors associated with deep (shallow) transparency practices in a group of 113 voluntary programs focused on sustainability.</t>
+  </si>
+  <si>
+    <t>The rise of “new” transnational governance has intensiﬁed debates about a lack of accountability in global politics. Reviewing the mechanisms through which transparency can foster accountability beyond the state, this article explores the determinants of information disclosure in the ﬁeld of transnational sustainability governance.</t>
+  </si>
+  <si>
+    <t>The spread of “new” transnational governance has prompted questions about its accountability. Without recourse to principal–agent forms of accountability, scholars and practitioners have proposed transparency as a potential solution. Yet as we have shown, very few studies have documented and explained variation in the practice of transparency in transnational governance. Our analysis contributes to ﬁlling this gap by examining internal and external factors associated with deep (shallow) transparency practices in a group of 113 voluntary programs focused on sustainability. Several ﬁndings and implications follow</t>
+  </si>
+  <si>
+    <t>Cashore
+Bo
+Ashwath
+Chris</t>
+  </si>
+  <si>
+    <t>doi:10.1111/rego.12111</t>
+  </si>
+  <si>
+    <t>The politics of resonance: Transnational sustainability governance in Argentina</t>
+  </si>
+  <si>
+    <t>Alejandro Milcíades Peña</t>
+  </si>
+  <si>
+    <t>Determinants of transnational private governance participation</t>
+  </si>
+  <si>
+    <t>Uses the argentinian case study to make observations in general about what determines transnational private governance participation</t>
+  </si>
+  <si>
+    <t>Analyzing the limited participation of Argentine actors in contemporary sustainability initiatives, the article claims that the validity and relevance of sustainability programs is affected by three dimensions of national political culture accentuated over the last decade: a politicized model of state-society relations, the low visibility of environmental matters, and a widespread anti-corporate culture. By examining the ideational fundamentals of the “politics of resonance” in Argentina, the article makes a relevant and original contribution to transnational regulation literature, highlighting the need for theoretical accounts and empirical analyses that address domestic and cultural variables as fundamental pieces in transnational norm diffusion and effectiveness.</t>
+  </si>
+  <si>
+    <t>Generalised conclusion/theories generated</t>
+  </si>
+  <si>
+    <t>By examining the ideational fundamentals of the “politics of resonance” in Argentina, the article makes a relevant and original contribution to transnational regulation literature, highlighting the need for theoretical accounts and empirical analyses that address domestic and cultural variables as fundamental pieces in transnational norm diffusion and effectiveness.</t>
+  </si>
+  <si>
+    <t>No utility discussed, seeks to explore transnational sustainability private governance in argentinian context. Themes like transparency and accountability are also part of the research framework</t>
+  </si>
+  <si>
+    <t>As an initial measure of salience, I analyze formal participation by Argentine actors in the organizational structures of three global sustainability initiatives: the UNGC, GRI, and ISO SR. These three initiatives possess four institutional features serving the study of resonance. First, albeit representing different types of frameworks, the three initiatives are recognized in the literature as central intermediaries in the sustainability ﬁeld and can be treated as institutional representatives of the sustainability agenda (Rasche 2009). 6 The initiatives share a focus on environmental protection, social beneﬁts, and economic viability; preference for market-based approaches; self-regulation and entrepreneurial authority; and advance values of inclusiveness, transparency, accountability, and deliberation (Bartley &amp; Smith 2010; Gilbert et al. 2011; Abbott 2012).</t>
+  </si>
+  <si>
+    <t>Concludes with implications on determinants of receptiveness to sustainability norms, no utility involved</t>
+  </si>
+  <si>
+    <t>Acknowledging the limitations of case studies for theory-building, the article poses that national cultural-ideological structures may be more resilient and inﬂuential than what conventional models imply, conﬁguring discursive ﬁelds that can be either supportive or detrimental for the operation of global norms and actors. Moreover, the case suggests that some national political cultures may be more compatible and receptive than others in relation to sustainability norms, and that such compatibility constitutes a necessary condition for successful norm diffusion and regime effectiveness upon implementation.</t>
+  </si>
+  <si>
+    <t>Type 3 (based on abstract)
+Looks at participation in private governance across countries. Doesnt seem to identify a specific on the ground problem. Looks at how transnational private governance regimes resonate at the domestic level based on a number of factors (politics, norms, culture)
+Goes beyond utillity and considers aspects like politics, national political culture, state-society relations, the low visibility of environmental matters, and a widespread anti-corporate culture</t>
   </si>
   <si>
     <t>doi:10.1111/rego.12138</t>
@@ -1781,7 +2182,33 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1792,6 +2219,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2091,7 +2522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87732B7A-3C80-8742-A5E5-22FC0EFC5C49}">
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -2108,52 +2539,52 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>398</v>
+        <v>521</v>
       </c>
       <c r="F1" t="s">
-        <v>399</v>
+        <v>522</v>
       </c>
       <c r="G1" t="s">
-        <v>400</v>
+        <v>523</v>
       </c>
       <c r="H1" t="s">
-        <v>401</v>
+        <v>524</v>
       </c>
       <c r="I1" t="s">
-        <v>402</v>
+        <v>525</v>
       </c>
       <c r="J1" t="s">
-        <v>403</v>
+        <v>526</v>
       </c>
       <c r="K1" t="s">
-        <v>404</v>
+        <v>527</v>
       </c>
       <c r="L1" t="s">
-        <v>405</v>
+        <v>528</v>
       </c>
       <c r="M1" t="s">
-        <v>406</v>
+        <v>529</v>
       </c>
       <c r="N1" t="s">
-        <v>407</v>
+        <v>530</v>
       </c>
       <c r="O1" t="s">
-        <v>408</v>
+        <v>531</v>
       </c>
       <c r="P1" t="s">
-        <v>409</v>
+        <v>532</v>
       </c>
       <c r="Q1" t="s">
-        <v>410</v>
+        <v>533</v>
       </c>
       <c r="R1" t="s">
-        <v>411</v>
+        <v>534</v>
       </c>
       <c r="S1" t="s">
-        <v>412</v>
+        <v>535</v>
       </c>
       <c r="T1" t="s">
-        <v>413</v>
+        <v>536</v>
       </c>
       <c r="U1" t="s">
         <v>4</v>
@@ -2176,1303 +2607,1306 @@
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="P2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="S2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="U2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="V2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="W2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="X2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="Z2" t="str">
+        <f>IF(V2=X2, "Match", "Non-Match")</f>
+        <v>Match</v>
       </c>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
+      <c r="Z3" t="s">
         <v>43</v>
-      </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" t="s">
-        <v>49</v>
-      </c>
-      <c r="M3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>52</v>
-      </c>
-      <c r="R3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U3" t="s">
-        <v>14</v>
-      </c>
-      <c r="V3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W3" t="s">
-        <v>18</v>
-      </c>
-      <c r="X3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" t="s">
         <v>53</v>
       </c>
-      <c r="C4" t="s">
+      <c r="P4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="s">
         <v>54</v>
       </c>
-      <c r="D4" t="s">
+      <c r="R4" t="s">
         <v>55</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" t="s">
         <v>56</v>
       </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="U4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" t="s">
+        <v>24</v>
+      </c>
+      <c r="W4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y4" t="s">
         <v>57</v>
       </c>
-      <c r="I4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" t="s">
-        <v>60</v>
-      </c>
-      <c r="M4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" t="s">
-        <v>61</v>
-      </c>
-      <c r="O4" t="s">
-        <v>62</v>
-      </c>
-      <c r="P4" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>63</v>
-      </c>
-      <c r="R4" t="s">
-        <v>64</v>
-      </c>
-      <c r="S4" t="s">
-        <v>16</v>
-      </c>
-      <c r="T4" t="s">
-        <v>13</v>
-      </c>
-      <c r="U4" t="s">
-        <v>14</v>
-      </c>
-      <c r="V4" t="s">
-        <v>16</v>
-      </c>
-      <c r="W4" t="s">
-        <v>65</v>
-      </c>
-      <c r="X4" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>66</v>
-      </c>
       <c r="Z4" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+      <c r="O5" t="s">
         <v>67</v>
       </c>
-      <c r="C5" t="s">
+      <c r="P5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="s">
         <v>68</v>
       </c>
-      <c r="D5" t="s">
+      <c r="R5" t="s">
         <v>69</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="S5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" t="s">
         <v>70</v>
       </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="U5" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" t="s">
+        <v>39</v>
+      </c>
+      <c r="W5" t="s">
         <v>71</v>
       </c>
-      <c r="I5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" t="s">
-        <v>73</v>
-      </c>
-      <c r="L5" t="s">
-        <v>74</v>
-      </c>
-      <c r="M5" t="s">
-        <v>11</v>
-      </c>
-      <c r="N5" t="s">
-        <v>75</v>
-      </c>
-      <c r="O5" t="s">
-        <v>76</v>
-      </c>
-      <c r="P5" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>77</v>
-      </c>
-      <c r="R5" t="s">
-        <v>78</v>
-      </c>
-      <c r="S5" t="s">
-        <v>79</v>
-      </c>
-      <c r="T5" t="s">
-        <v>21</v>
-      </c>
-      <c r="U5" t="s">
-        <v>14</v>
-      </c>
-      <c r="V5" t="s">
-        <v>16</v>
-      </c>
-      <c r="W5" t="s">
-        <v>80</v>
-      </c>
       <c r="X5" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="Y5" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="Z5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" t="s">
         <v>82</v>
       </c>
-      <c r="C6" t="s">
+      <c r="P6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="s">
         <v>83</v>
       </c>
-      <c r="D6" t="s">
+      <c r="R6" t="s">
         <v>84</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="S6" t="s">
         <v>85</v>
       </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="T6" t="s">
+        <v>25</v>
+      </c>
+      <c r="U6" t="s">
+        <v>26</v>
+      </c>
+      <c r="V6" t="s">
+        <v>24</v>
+      </c>
+      <c r="W6" t="s">
+        <v>41</v>
+      </c>
+      <c r="X6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y6" t="s">
         <v>86</v>
       </c>
-      <c r="I6" t="s">
+      <c r="Z6" t="s">
         <v>87</v>
-      </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M6" t="s">
-        <v>11</v>
-      </c>
-      <c r="N6" t="s">
-        <v>90</v>
-      </c>
-      <c r="O6" t="s">
-        <v>91</v>
-      </c>
-      <c r="P6" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>92</v>
-      </c>
-      <c r="R6" t="s">
-        <v>93</v>
-      </c>
-      <c r="S6" t="s">
-        <v>16</v>
-      </c>
-      <c r="T6" t="s">
-        <v>26</v>
-      </c>
-      <c r="U6" t="s">
-        <v>14</v>
-      </c>
-      <c r="V6" t="s">
-        <v>16</v>
-      </c>
-      <c r="W6" t="s">
-        <v>18</v>
-      </c>
-      <c r="X6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" t="s">
+        <v>92</v>
+      </c>
+      <c r="L7" t="s">
+        <v>94</v>
+      </c>
+      <c r="M7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" t="s">
         <v>95</v>
       </c>
-      <c r="C7" t="s">
+      <c r="O7" t="s">
         <v>96</v>
       </c>
-      <c r="D7" t="s">
+      <c r="P7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q7" t="s">
         <v>97</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="R7" t="s">
         <v>98</v>
       </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="S7" t="s">
+        <v>85</v>
+      </c>
+      <c r="T7" t="s">
+        <v>25</v>
+      </c>
+      <c r="U7" t="s">
+        <v>26</v>
+      </c>
+      <c r="V7" t="s">
+        <v>24</v>
+      </c>
+      <c r="W7" t="s">
         <v>99</v>
       </c>
-      <c r="I7" t="s">
+      <c r="X7" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y7" t="s">
         <v>100</v>
       </c>
-      <c r="J7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" t="s">
-        <v>101</v>
-      </c>
-      <c r="L7" t="s">
-        <v>102</v>
-      </c>
-      <c r="M7" t="s">
-        <v>10</v>
-      </c>
-      <c r="N7" t="s">
-        <v>103</v>
-      </c>
-      <c r="O7" t="s">
-        <v>104</v>
-      </c>
-      <c r="P7" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>105</v>
-      </c>
-      <c r="R7" t="s">
-        <v>106</v>
-      </c>
-      <c r="S7" t="s">
-        <v>12</v>
-      </c>
-      <c r="T7" t="s">
-        <v>26</v>
-      </c>
-      <c r="U7" t="s">
-        <v>14</v>
-      </c>
-      <c r="V7" t="s">
-        <v>12</v>
-      </c>
-      <c r="W7" t="s">
-        <v>15</v>
-      </c>
-      <c r="X7" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>107</v>
-      </c>
       <c r="Z7" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L8" t="s">
         <v>108</v>
       </c>
-      <c r="C8" t="s">
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" t="s">
         <v>109</v>
       </c>
-      <c r="D8" t="s">
+      <c r="O8" t="s">
+        <v>110</v>
+      </c>
+      <c r="P8" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="s">
         <v>111</v>
       </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="R8" t="s">
         <v>112</v>
       </c>
-      <c r="G8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" t="s">
-        <v>114</v>
-      </c>
-      <c r="J8" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" t="s">
-        <v>115</v>
-      </c>
-      <c r="L8" t="s">
-        <v>116</v>
-      </c>
-      <c r="M8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N8" t="s">
-        <v>117</v>
-      </c>
-      <c r="O8" t="s">
-        <v>118</v>
-      </c>
-      <c r="P8" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>119</v>
-      </c>
-      <c r="R8" t="s">
-        <v>120</v>
-      </c>
       <c r="S8" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="T8" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="U8" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="V8" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="W8" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="X8" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Y8" t="s">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="Z8" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" t="s">
+        <v>119</v>
+      </c>
+      <c r="L9" t="s">
+        <v>120</v>
+      </c>
+      <c r="M9" t="s">
+        <v>15</v>
+      </c>
+      <c r="N9" t="s">
+        <v>121</v>
+      </c>
+      <c r="O9" t="s">
         <v>122</v>
       </c>
-      <c r="C9" t="s">
+      <c r="P9" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="s">
         <v>123</v>
       </c>
-      <c r="D9" t="s">
+      <c r="R9" t="s">
+        <v>120</v>
+      </c>
+      <c r="S9" t="s">
+        <v>39</v>
+      </c>
+      <c r="T9" t="s">
         <v>124</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="U9" t="s">
+        <v>26</v>
+      </c>
+      <c r="V9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" t="s">
         <v>125</v>
       </c>
-      <c r="G9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="X9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y9" t="s">
         <v>126</v>
       </c>
-      <c r="I9" t="s">
-        <v>127</v>
-      </c>
-      <c r="J9" t="s">
-        <v>11</v>
-      </c>
-      <c r="K9" t="s">
-        <v>128</v>
-      </c>
-      <c r="L9" t="s">
-        <v>129</v>
-      </c>
-      <c r="M9" t="s">
-        <v>11</v>
-      </c>
-      <c r="N9" t="s">
-        <v>130</v>
-      </c>
-      <c r="O9" t="s">
-        <v>131</v>
-      </c>
-      <c r="P9" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>132</v>
-      </c>
-      <c r="R9" t="s">
-        <v>129</v>
-      </c>
-      <c r="S9" t="s">
-        <v>79</v>
-      </c>
-      <c r="T9" t="s">
-        <v>13</v>
-      </c>
-      <c r="U9" t="s">
-        <v>14</v>
-      </c>
-      <c r="V9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W9" t="s">
-        <v>133</v>
-      </c>
-      <c r="X9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>79</v>
-      </c>
       <c r="Z9" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I10" t="s">
+        <v>133</v>
+      </c>
+      <c r="J10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" t="s">
         <v>134</v>
       </c>
-      <c r="C10" t="s">
+      <c r="L10" t="s">
         <v>135</v>
       </c>
-      <c r="D10" t="s">
+      <c r="M10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" t="s">
+        <v>109</v>
+      </c>
+      <c r="O10" t="s">
         <v>136</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="P10" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>111</v>
+      </c>
+      <c r="R10" t="s">
         <v>137</v>
       </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="S10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T10" t="s">
+        <v>70</v>
+      </c>
+      <c r="U10" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" t="s">
+        <v>39</v>
+      </c>
+      <c r="W10" t="s">
         <v>138</v>
       </c>
-      <c r="I10" t="s">
-        <v>139</v>
-      </c>
-      <c r="J10" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" t="s">
-        <v>140</v>
-      </c>
-      <c r="L10" t="s">
-        <v>141</v>
-      </c>
-      <c r="M10" t="s">
-        <v>11</v>
-      </c>
-      <c r="N10" t="s">
-        <v>142</v>
-      </c>
-      <c r="O10" t="s">
-        <v>143</v>
-      </c>
-      <c r="P10" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>144</v>
-      </c>
-      <c r="R10" t="s">
-        <v>145</v>
-      </c>
-      <c r="S10" t="s">
-        <v>16</v>
-      </c>
-      <c r="T10" t="s">
-        <v>13</v>
-      </c>
-      <c r="U10" t="s">
-        <v>14</v>
-      </c>
-      <c r="V10" t="s">
-        <v>16</v>
-      </c>
-      <c r="W10" t="s">
-        <v>18</v>
-      </c>
       <c r="X10" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Y10" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="Z10" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" t="s">
+        <v>144</v>
+      </c>
+      <c r="J11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" t="s">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" t="s">
         <v>147</v>
       </c>
-      <c r="C11" t="s">
+      <c r="O11" t="s">
         <v>148</v>
       </c>
-      <c r="D11" t="s">
+      <c r="P11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q11" t="s">
         <v>149</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="R11" t="s">
         <v>150</v>
       </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="S11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T11" t="s">
+        <v>124</v>
+      </c>
+      <c r="U11" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" t="s">
+        <v>39</v>
+      </c>
+      <c r="W11" t="s">
+        <v>41</v>
+      </c>
+      <c r="X11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y11" t="s">
         <v>151</v>
       </c>
-      <c r="I11" t="s">
-        <v>152</v>
-      </c>
-      <c r="J11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" t="s">
-        <v>153</v>
-      </c>
-      <c r="L11" t="s">
-        <v>154</v>
-      </c>
-      <c r="M11" t="s">
-        <v>11</v>
-      </c>
-      <c r="N11" t="s">
-        <v>155</v>
-      </c>
-      <c r="O11" t="s">
-        <v>156</v>
-      </c>
-      <c r="P11" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>157</v>
-      </c>
-      <c r="R11" t="s">
-        <v>158</v>
-      </c>
-      <c r="S11" t="s">
-        <v>16</v>
-      </c>
-      <c r="T11" t="s">
-        <v>26</v>
-      </c>
-      <c r="U11" t="s">
-        <v>14</v>
-      </c>
-      <c r="V11" t="s">
-        <v>16</v>
-      </c>
-      <c r="W11" t="s">
-        <v>159</v>
-      </c>
-      <c r="X11" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>16</v>
-      </c>
       <c r="Z11" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>156</v>
+      </c>
+      <c r="I12" t="s">
+        <v>157</v>
+      </c>
+      <c r="J12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" t="s">
+        <v>158</v>
+      </c>
+      <c r="L12" t="s">
+        <v>159</v>
+      </c>
+      <c r="M12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" t="s">
         <v>160</v>
       </c>
-      <c r="C12" t="s">
+      <c r="O12" t="s">
         <v>161</v>
       </c>
-      <c r="D12" t="s">
+      <c r="P12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" t="s">
         <v>162</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="R12" t="s">
         <v>163</v>
       </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="S12" t="s">
+        <v>24</v>
+      </c>
+      <c r="T12" t="s">
+        <v>25</v>
+      </c>
+      <c r="U12" t="s">
+        <v>26</v>
+      </c>
+      <c r="V12" t="s">
+        <v>24</v>
+      </c>
+      <c r="W12" t="s">
+        <v>41</v>
+      </c>
+      <c r="X12" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y12" t="s">
         <v>164</v>
       </c>
-      <c r="I12" t="s">
-        <v>165</v>
-      </c>
-      <c r="J12" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" t="s">
-        <v>166</v>
-      </c>
-      <c r="L12" t="s">
-        <v>167</v>
-      </c>
-      <c r="M12" t="s">
-        <v>11</v>
-      </c>
-      <c r="N12" t="s">
-        <v>168</v>
-      </c>
-      <c r="O12" t="s">
-        <v>169</v>
-      </c>
-      <c r="P12" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>170</v>
-      </c>
-      <c r="R12" t="s">
-        <v>167</v>
-      </c>
-      <c r="S12" t="s">
-        <v>16</v>
-      </c>
-      <c r="T12" t="s">
-        <v>13</v>
-      </c>
-      <c r="U12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V12" t="s">
-        <v>16</v>
-      </c>
-      <c r="W12" t="s">
-        <v>171</v>
-      </c>
-      <c r="X12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>16</v>
-      </c>
       <c r="Z12" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>168</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>169</v>
+      </c>
+      <c r="I13" t="s">
+        <v>170</v>
+      </c>
+      <c r="J13" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" t="s">
+        <v>171</v>
+      </c>
+      <c r="L13" t="s">
         <v>172</v>
       </c>
-      <c r="C13" t="s">
+      <c r="M13" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" t="s">
         <v>173</v>
       </c>
-      <c r="D13" t="s">
+      <c r="O13" t="s">
         <v>174</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="P13" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="s">
         <v>175</v>
       </c>
-      <c r="G13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" t="s">
-        <v>176</v>
-      </c>
-      <c r="I13" t="s">
-        <v>177</v>
-      </c>
-      <c r="J13" t="s">
-        <v>11</v>
-      </c>
-      <c r="K13" t="s">
-        <v>176</v>
-      </c>
-      <c r="L13" t="s">
-        <v>178</v>
-      </c>
-      <c r="M13" t="s">
-        <v>11</v>
-      </c>
-      <c r="N13" t="s">
-        <v>179</v>
-      </c>
-      <c r="O13" t="s">
-        <v>180</v>
-      </c>
-      <c r="P13" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>181</v>
-      </c>
       <c r="R13" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="S13" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="T13" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="U13" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="V13" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="W13" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="X13" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="Y13" t="s">
-        <v>183</v>
+        <v>42</v>
       </c>
       <c r="Z13" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>180</v>
+      </c>
+      <c r="I14" t="s">
+        <v>181</v>
+      </c>
+      <c r="J14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" t="s">
+        <v>183</v>
+      </c>
+      <c r="M14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" t="s">
         <v>184</v>
       </c>
-      <c r="C14" t="s">
+      <c r="O14" t="s">
         <v>185</v>
       </c>
-      <c r="D14" t="s">
+      <c r="P14" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q14" t="s">
         <v>186</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="R14" t="s">
         <v>187</v>
       </c>
-      <c r="G14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="S14" t="s">
+        <v>39</v>
+      </c>
+      <c r="T14" t="s">
+        <v>25</v>
+      </c>
+      <c r="U14" t="s">
+        <v>26</v>
+      </c>
+      <c r="V14" t="s">
+        <v>39</v>
+      </c>
+      <c r="W14" t="s">
         <v>188</v>
       </c>
-      <c r="I14" t="s">
+      <c r="X14" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y14" t="s">
         <v>189</v>
       </c>
-      <c r="J14" t="s">
-        <v>11</v>
-      </c>
-      <c r="K14" t="s">
-        <v>188</v>
-      </c>
-      <c r="L14" t="s">
-        <v>190</v>
-      </c>
-      <c r="M14" t="s">
-        <v>11</v>
-      </c>
-      <c r="N14" t="s">
-        <v>191</v>
-      </c>
-      <c r="O14" t="s">
-        <v>192</v>
-      </c>
-      <c r="P14" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>193</v>
-      </c>
-      <c r="R14" t="s">
-        <v>194</v>
-      </c>
-      <c r="S14" t="s">
-        <v>79</v>
-      </c>
-      <c r="T14" t="s">
-        <v>17</v>
-      </c>
-      <c r="U14" t="s">
-        <v>14</v>
-      </c>
-      <c r="V14" t="s">
-        <v>16</v>
-      </c>
-      <c r="W14" t="s">
-        <v>18</v>
-      </c>
-      <c r="X14" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>195</v>
-      </c>
       <c r="Z14" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>193</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>194</v>
+      </c>
+      <c r="I15" t="s">
+        <v>195</v>
+      </c>
+      <c r="J15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" t="s">
         <v>196</v>
       </c>
-      <c r="C15" t="s">
+      <c r="L15" t="s">
         <v>197</v>
       </c>
-      <c r="D15" t="s">
+      <c r="M15" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" t="s">
         <v>198</v>
       </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="O15" t="s">
         <v>199</v>
       </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="P15" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" t="s">
         <v>200</v>
       </c>
-      <c r="I15"/>
-      <c r="J15" t="s">
-        <v>10</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="R15" t="s">
         <v>201</v>
       </c>
-      <c r="L15" t="s">
+      <c r="S15" t="s">
         <v>202</v>
       </c>
-      <c r="M15" t="s">
-        <v>11</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="T15" t="s">
+        <v>70</v>
+      </c>
+      <c r="U15" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" t="s">
+        <v>39</v>
+      </c>
+      <c r="W15" t="s">
         <v>203</v>
       </c>
-      <c r="O15" t="s">
+      <c r="X15" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y15" t="s">
         <v>204</v>
       </c>
-      <c r="P15" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>205</v>
-      </c>
-      <c r="R15" t="s">
-        <v>206</v>
-      </c>
-      <c r="S15" t="s">
-        <v>16</v>
-      </c>
-      <c r="T15" t="s">
-        <v>21</v>
-      </c>
-      <c r="U15" t="s">
-        <v>14</v>
-      </c>
-      <c r="V15" t="s">
-        <v>16</v>
-      </c>
-      <c r="W15" t="s">
-        <v>18</v>
-      </c>
-      <c r="X15" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>16</v>
-      </c>
       <c r="Z15" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" t="s">
         <v>207</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
         <v>208</v>
       </c>
-      <c r="D16" t="s">
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
         <v>209</v>
       </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="I16" t="s">
         <v>210</v>
       </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" t="s">
         <v>211</v>
       </c>
-      <c r="I16" t="s">
+      <c r="L16" t="s">
         <v>212</v>
       </c>
-      <c r="J16" t="s">
-        <v>10</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="M16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16" t="s">
         <v>213</v>
       </c>
-      <c r="L16" t="s">
+      <c r="O16" t="s">
         <v>214</v>
       </c>
-      <c r="M16" t="s">
-        <v>11</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="P16" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q16" t="s">
         <v>215</v>
       </c>
-      <c r="O16" t="s">
+      <c r="R16" t="s">
         <v>216</v>
       </c>
-      <c r="P16" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="S16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T16" t="s">
+        <v>124</v>
+      </c>
+      <c r="U16" t="s">
+        <v>26</v>
+      </c>
+      <c r="V16" t="s">
+        <v>39</v>
+      </c>
+      <c r="W16" t="s">
+        <v>41</v>
+      </c>
+      <c r="X16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y16" t="s">
         <v>217</v>
       </c>
-      <c r="R16" t="s">
-        <v>218</v>
-      </c>
-      <c r="S16" t="s">
-        <v>16</v>
-      </c>
-      <c r="T16" t="s">
-        <v>26</v>
-      </c>
-      <c r="U16" t="s">
-        <v>14</v>
-      </c>
-      <c r="V16" t="s">
-        <v>16</v>
-      </c>
-      <c r="W16" t="s">
-        <v>22</v>
-      </c>
-      <c r="X16" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>16</v>
-      </c>
       <c r="Z16" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D17" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>221</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>222</v>
+      </c>
+      <c r="I17" t="s">
+        <v>223</v>
+      </c>
+      <c r="J17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" t="s">
+        <v>224</v>
+      </c>
+      <c r="L17" t="s">
+        <v>225</v>
+      </c>
+      <c r="M17" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" t="s">
+        <v>226</v>
+      </c>
+      <c r="O17" t="s">
+        <v>227</v>
+      </c>
+      <c r="P17" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>228</v>
+      </c>
+      <c r="R17" t="s">
+        <v>229</v>
+      </c>
+      <c r="S17" t="s">
+        <v>24</v>
+      </c>
+      <c r="T17" t="s">
+        <v>124</v>
+      </c>
+      <c r="U17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" t="s">
-        <v>219</v>
-      </c>
-      <c r="C17" t="s">
-        <v>220</v>
-      </c>
-      <c r="D17" t="s">
-        <v>221</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>222</v>
-      </c>
-      <c r="G17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" t="s">
-        <v>223</v>
-      </c>
-      <c r="I17" t="s">
-        <v>224</v>
-      </c>
-      <c r="J17" t="s">
-        <v>10</v>
-      </c>
-      <c r="K17" t="s">
-        <v>225</v>
-      </c>
-      <c r="L17" t="s">
-        <v>226</v>
-      </c>
-      <c r="M17" t="s">
-        <v>11</v>
-      </c>
-      <c r="N17" t="s">
-        <v>227</v>
-      </c>
-      <c r="O17" t="s">
-        <v>228</v>
-      </c>
-      <c r="P17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>229</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="V17" t="s">
+        <v>24</v>
+      </c>
+      <c r="W17" t="s">
+        <v>27</v>
+      </c>
+      <c r="X17" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y17" t="s">
         <v>230</v>
       </c>
-      <c r="S17" t="s">
-        <v>16</v>
-      </c>
-      <c r="T17" t="s">
-        <v>21</v>
-      </c>
-      <c r="U17" t="s">
-        <v>14</v>
-      </c>
-      <c r="V17" t="s">
-        <v>16</v>
-      </c>
-      <c r="W17" t="s">
-        <v>65</v>
-      </c>
-      <c r="X17" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>231</v>
-      </c>
       <c r="Z17" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" t="s">
         <v>232</v>
-      </c>
-      <c r="C18" t="s">
-        <v>233</v>
       </c>
       <c r="D18" t="s">
         <v>234</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
         <v>235</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
         <v>236</v>
@@ -3481,7 +3915,7 @@
         <v>237</v>
       </c>
       <c r="J18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K18" t="s">
         <v>238</v>
@@ -3490,7 +3924,7 @@
         <v>239</v>
       </c>
       <c r="M18" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N18" t="s">
         <v>240</v>
@@ -3499,122 +3933,122 @@
         <v>241</v>
       </c>
       <c r="P18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q18" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="R18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="S18" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="T18" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="U18" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="V18" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="W18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="X18" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Y18" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="Z18" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C19" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J19" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M19" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N19" t="s">
+        <v>253</v>
+      </c>
+      <c r="O19" t="s">
+        <v>254</v>
+      </c>
+      <c r="P19" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>255</v>
+      </c>
+      <c r="R19" t="s">
         <v>252</v>
       </c>
-      <c r="O19" t="s">
-        <v>253</v>
-      </c>
-      <c r="P19" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>254</v>
-      </c>
-      <c r="R19" t="s">
-        <v>255</v>
-      </c>
       <c r="S19" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
       <c r="T19" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="U19" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="V19" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
       <c r="W19" t="s">
-        <v>15</v>
+        <v>256</v>
       </c>
       <c r="X19" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
       <c r="Y19" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="Z19" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>257</v>
@@ -3623,941 +4057,1739 @@
         <v>258</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>259</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="s">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="R20" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="S20" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="T20" t="s">
+        <v>25</v>
+      </c>
+      <c r="U20" t="s">
         <v>26</v>
       </c>
-      <c r="U20" t="s">
-        <v>18</v>
-      </c>
       <c r="V20" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="W20" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="X20" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Y20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O21" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q21" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="R21" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="S21" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="T21" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="U21" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V21" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="W21" t="s">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="X21" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Y21" t="s">
-        <v>280</v>
+        <v>39</v>
       </c>
       <c r="Z21" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>285</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="L22" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="M22" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N22" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O22" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="P22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="R22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="S22" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="T22" t="s">
+        <v>25</v>
+      </c>
+      <c r="U22" t="s">
         <v>26</v>
       </c>
-      <c r="U22" t="s">
-        <v>18</v>
-      </c>
       <c r="V22" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W22" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="X22" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Y22" t="s">
-        <v>290</v>
+        <v>39</v>
       </c>
       <c r="Z22" t="s">
-        <v>291</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C23" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F23" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I23" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J23" t="s">
-        <v>11</v>
-      </c>
-      <c r="K23"/>
-      <c r="L23"/>
+        <v>15</v>
+      </c>
+      <c r="K23" t="s">
+        <v>299</v>
+      </c>
+      <c r="L23" t="s">
+        <v>301</v>
+      </c>
       <c r="M23" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N23" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="O23" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="P23" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="s">
-        <v>298</v>
-      </c>
-      <c r="R23"/>
+        <v>304</v>
+      </c>
+      <c r="R23" t="s">
+        <v>305</v>
+      </c>
       <c r="S23" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="T23" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="U23" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V23" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="W23" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="X23" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="Y23" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="Z23" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C24" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D24" t="s">
-        <v>246</v>
+        <v>309</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="I24" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="J24" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>306</v>
-      </c>
-      <c r="L24"/>
+        <v>311</v>
+      </c>
+      <c r="L24" t="s">
+        <v>313</v>
+      </c>
       <c r="M24" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N24" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="O24" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="P24" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q24" t="s">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="R24" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="S24" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
       <c r="T24" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="U24" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V24" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W24" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="X24" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
       <c r="Y24" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="Z24" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C25" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D25" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>315</v>
-      </c>
-      <c r="I25" t="s">
-        <v>316</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="I25"/>
       <c r="J25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="L25" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="M25" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N25" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="O25" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="P25" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q25" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="R25" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="S25" t="s">
-        <v>12</v>
-      </c>
-      <c r="T25"/>
+        <v>39</v>
+      </c>
+      <c r="T25" t="s">
+        <v>70</v>
+      </c>
       <c r="U25" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V25" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W25" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="X25" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="Y25" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="Z25" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C26" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D26" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="I26" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="J26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K26" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="L26" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="M26" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N26" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="O26" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="P26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q26" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="R26" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="S26" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="T26" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="U26" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V26" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="W26" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="X26" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Y26" t="s">
-        <v>335</v>
+        <v>39</v>
       </c>
       <c r="Z26" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C27" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D27" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="I27" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="J27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K27" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="L27" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="M27" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N27" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="O27" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="P27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q27" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="R27" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="S27" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="T27" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="U27" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V27" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="W27" t="s">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="X27" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="Y27" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Z27" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C28" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D28" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="G28" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="I28" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="J28" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="L28" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="M28" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N28" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="O28" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="P28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q28" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="R28" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="S28" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="T28" t="s">
+        <v>70</v>
+      </c>
+      <c r="U28" t="s">
         <v>26</v>
       </c>
-      <c r="U28" t="s">
-        <v>18</v>
-      </c>
       <c r="V28" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="W28" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="X28" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="Y28" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="Z28" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C29" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="D29" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="G29" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="I29" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="J29" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="L29" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="M29" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N29" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="O29" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="P29" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q29" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="R29" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="S29" t="s">
-        <v>16</v>
-      </c>
-      <c r="T29"/>
+        <v>24</v>
+      </c>
+      <c r="T29" t="s">
+        <v>25</v>
+      </c>
       <c r="U29" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V29" t="s">
-        <v>370</v>
+        <v>24</v>
       </c>
       <c r="W29" t="s">
         <v>27</v>
       </c>
       <c r="X29" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Y29" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="Z29" t="s">
-        <v>291</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C30" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D30" t="s">
-        <v>374</v>
+        <v>192</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="I30" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="J30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="L30" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="M30" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N30" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="O30" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="P30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="s">
-        <v>382</v>
+        <v>328</v>
       </c>
       <c r="R30" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="S30" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="T30" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="U30" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="V30" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="W30" t="s">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="X30" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="Y30" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="Z30" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>391</v>
+      </c>
+      <c r="C31" t="s">
+        <v>392</v>
+      </c>
+      <c r="D31" t="s">
+        <v>393</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>394</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>395</v>
+      </c>
+      <c r="I31" t="s">
+        <v>396</v>
+      </c>
+      <c r="J31" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" t="s">
+        <v>397</v>
+      </c>
+      <c r="L31" t="s">
+        <v>398</v>
+      </c>
+      <c r="M31" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" t="s">
+        <v>399</v>
+      </c>
+      <c r="O31" t="s">
+        <v>400</v>
+      </c>
+      <c r="P31" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>401</v>
+      </c>
+      <c r="R31" t="s">
+        <v>402</v>
+      </c>
+      <c r="S31" t="s">
+        <v>39</v>
+      </c>
+      <c r="T31" t="s">
+        <v>25</v>
+      </c>
+      <c r="U31" t="s">
+        <v>41</v>
+      </c>
+      <c r="V31" t="s">
+        <v>39</v>
+      </c>
+      <c r="W31" t="s">
+        <v>203</v>
+      </c>
+      <c r="X31" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>404</v>
+      </c>
+      <c r="C32" t="s">
+        <v>405</v>
+      </c>
+      <c r="D32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
+        <v>406</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>407</v>
+      </c>
+      <c r="I32" t="s">
+        <v>408</v>
+      </c>
+      <c r="J32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" t="s">
+        <v>407</v>
+      </c>
+      <c r="L32" t="s">
+        <v>409</v>
+      </c>
+      <c r="M32" t="s">
+        <v>15</v>
+      </c>
+      <c r="N32" t="s">
+        <v>410</v>
+      </c>
+      <c r="O32" t="s">
+        <v>411</v>
+      </c>
+      <c r="P32" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>410</v>
+      </c>
+      <c r="R32" t="s">
+        <v>411</v>
+      </c>
+      <c r="S32" t="s">
+        <v>39</v>
+      </c>
+      <c r="T32" t="s">
+        <v>124</v>
+      </c>
+      <c r="U32" t="s">
+        <v>41</v>
+      </c>
+      <c r="V32" t="s">
+        <v>24</v>
+      </c>
+      <c r="W32" t="s">
+        <v>412</v>
+      </c>
+      <c r="X32" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>413</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>415</v>
+      </c>
+      <c r="C33" t="s">
+        <v>416</v>
+      </c>
+      <c r="D33" t="s">
+        <v>417</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>418</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>419</v>
+      </c>
+      <c r="I33" t="s">
+        <v>420</v>
+      </c>
+      <c r="J33" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N33" t="s">
+        <v>421</v>
+      </c>
+      <c r="O33" t="s">
+        <v>422</v>
+      </c>
+      <c r="P33" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>421</v>
+      </c>
+      <c r="R33"/>
+      <c r="S33" t="s">
+        <v>85</v>
+      </c>
+      <c r="T33" t="s">
+        <v>70</v>
+      </c>
+      <c r="U33" t="s">
+        <v>41</v>
+      </c>
+      <c r="V33" t="s">
+        <v>85</v>
+      </c>
+      <c r="W33" t="s">
+        <v>203</v>
+      </c>
+      <c r="X33" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>423</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>424</v>
+      </c>
+      <c r="C34" t="s">
+        <v>425</v>
+      </c>
+      <c r="D34" t="s">
+        <v>369</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>426</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>427</v>
+      </c>
+      <c r="I34" t="s">
+        <v>428</v>
+      </c>
+      <c r="J34" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" t="s">
+        <v>429</v>
+      </c>
+      <c r="L34"/>
+      <c r="M34" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34" t="s">
+        <v>430</v>
+      </c>
+      <c r="O34" t="s">
+        <v>431</v>
+      </c>
+      <c r="P34" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>233</v>
+      </c>
+      <c r="R34" t="s">
+        <v>432</v>
+      </c>
+      <c r="S34" t="s">
+        <v>24</v>
+      </c>
+      <c r="T34" t="s">
+        <v>70</v>
+      </c>
+      <c r="U34" t="s">
+        <v>41</v>
+      </c>
+      <c r="V34" t="s">
+        <v>24</v>
+      </c>
+      <c r="W34" t="s">
+        <v>203</v>
+      </c>
+      <c r="X34" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>433</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>434</v>
+      </c>
+      <c r="C35" t="s">
+        <v>435</v>
+      </c>
+      <c r="D35" t="s">
+        <v>436</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" t="s">
+        <v>437</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>438</v>
+      </c>
+      <c r="I35" t="s">
+        <v>439</v>
+      </c>
+      <c r="J35" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" t="s">
+        <v>440</v>
+      </c>
+      <c r="L35" t="s">
+        <v>441</v>
+      </c>
+      <c r="M35" t="s">
+        <v>13</v>
+      </c>
+      <c r="N35" t="s">
+        <v>442</v>
+      </c>
+      <c r="O35" t="s">
+        <v>443</v>
+      </c>
+      <c r="P35" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>444</v>
+      </c>
+      <c r="R35" t="s">
+        <v>445</v>
+      </c>
+      <c r="S35" t="s">
+        <v>24</v>
+      </c>
+      <c r="T35"/>
+      <c r="U35" t="s">
+        <v>41</v>
+      </c>
+      <c r="V35" t="s">
+        <v>24</v>
+      </c>
+      <c r="W35" t="s">
+        <v>125</v>
+      </c>
+      <c r="X35" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>446</v>
+      </c>
+      <c r="C36" t="s">
+        <v>447</v>
+      </c>
+      <c r="D36" t="s">
+        <v>448</v>
+      </c>
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s">
+        <v>449</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>450</v>
+      </c>
+      <c r="I36" t="s">
+        <v>451</v>
+      </c>
+      <c r="J36" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" t="s">
+        <v>452</v>
+      </c>
+      <c r="L36" t="s">
+        <v>453</v>
+      </c>
+      <c r="M36" t="s">
+        <v>15</v>
+      </c>
+      <c r="N36" t="s">
+        <v>454</v>
+      </c>
+      <c r="O36" t="s">
+        <v>455</v>
+      </c>
+      <c r="P36" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>456</v>
+      </c>
+      <c r="R36" t="s">
+        <v>457</v>
+      </c>
+      <c r="S36" t="s">
+        <v>39</v>
+      </c>
+      <c r="T36" t="s">
         <v>40</v>
       </c>
-      <c r="B31" t="s">
-        <v>385</v>
-      </c>
-      <c r="C31" t="s">
-        <v>386</v>
-      </c>
-      <c r="D31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>387</v>
-      </c>
-      <c r="G31" t="s">
-        <v>10</v>
-      </c>
-      <c r="H31" t="s">
-        <v>388</v>
-      </c>
-      <c r="I31" t="s">
-        <v>389</v>
-      </c>
-      <c r="J31" t="s">
-        <v>11</v>
-      </c>
-      <c r="K31" t="s">
-        <v>390</v>
-      </c>
-      <c r="L31" t="s">
-        <v>391</v>
-      </c>
-      <c r="M31" t="s">
-        <v>11</v>
-      </c>
-      <c r="N31" t="s">
-        <v>392</v>
-      </c>
-      <c r="O31" t="s">
-        <v>393</v>
-      </c>
-      <c r="P31" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>394</v>
-      </c>
-      <c r="R31" t="s">
-        <v>395</v>
-      </c>
-      <c r="S31" t="s">
-        <v>79</v>
-      </c>
-      <c r="T31" t="s">
-        <v>26</v>
-      </c>
-      <c r="U31" t="s">
-        <v>80</v>
-      </c>
-      <c r="V31" t="s">
-        <v>79</v>
-      </c>
-      <c r="W31" t="s">
-        <v>396</v>
-      </c>
-      <c r="X31" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>20</v>
+      <c r="U36" t="s">
+        <v>41</v>
+      </c>
+      <c r="V36" t="s">
+        <v>39</v>
+      </c>
+      <c r="W36" t="s">
+        <v>188</v>
+      </c>
+      <c r="X36" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>458</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>459</v>
+      </c>
+      <c r="C37" t="s">
+        <v>460</v>
+      </c>
+      <c r="D37" t="s">
+        <v>461</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
+        <v>462</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>463</v>
+      </c>
+      <c r="I37" t="s">
+        <v>464</v>
+      </c>
+      <c r="J37" t="s">
+        <v>13</v>
+      </c>
+      <c r="K37" t="s">
+        <v>463</v>
+      </c>
+      <c r="L37" t="s">
+        <v>465</v>
+      </c>
+      <c r="M37" t="s">
+        <v>15</v>
+      </c>
+      <c r="N37" t="s">
+        <v>466</v>
+      </c>
+      <c r="O37" t="s">
+        <v>467</v>
+      </c>
+      <c r="P37" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>466</v>
+      </c>
+      <c r="R37" t="s">
+        <v>468</v>
+      </c>
+      <c r="S37" t="s">
+        <v>39</v>
+      </c>
+      <c r="T37" t="s">
+        <v>70</v>
+      </c>
+      <c r="U37" t="s">
+        <v>41</v>
+      </c>
+      <c r="V37" t="s">
+        <v>39</v>
+      </c>
+      <c r="W37" t="s">
+        <v>203</v>
+      </c>
+      <c r="X37" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>470</v>
+      </c>
+      <c r="C38" t="s">
+        <v>471</v>
+      </c>
+      <c r="D38" t="s">
+        <v>472</v>
+      </c>
+      <c r="E38" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
+        <v>473</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" t="s">
+        <v>474</v>
+      </c>
+      <c r="I38" t="s">
+        <v>475</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" t="s">
+        <v>476</v>
+      </c>
+      <c r="L38" t="s">
+        <v>477</v>
+      </c>
+      <c r="M38" t="s">
+        <v>15</v>
+      </c>
+      <c r="N38" t="s">
+        <v>478</v>
+      </c>
+      <c r="O38" t="s">
+        <v>479</v>
+      </c>
+      <c r="P38" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>480</v>
+      </c>
+      <c r="R38" t="s">
+        <v>481</v>
+      </c>
+      <c r="S38" t="s">
+        <v>202</v>
+      </c>
+      <c r="T38" t="s">
+        <v>124</v>
+      </c>
+      <c r="U38" t="s">
+        <v>41</v>
+      </c>
+      <c r="V38" t="s">
+        <v>202</v>
+      </c>
+      <c r="W38" t="s">
+        <v>125</v>
+      </c>
+      <c r="X38" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>482</v>
+      </c>
+      <c r="C39" t="s">
+        <v>483</v>
+      </c>
+      <c r="D39" t="s">
+        <v>484</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" t="s">
+        <v>485</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>486</v>
+      </c>
+      <c r="I39" t="s">
+        <v>487</v>
+      </c>
+      <c r="J39" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" t="s">
+        <v>488</v>
+      </c>
+      <c r="L39" t="s">
+        <v>489</v>
+      </c>
+      <c r="M39" t="s">
+        <v>15</v>
+      </c>
+      <c r="N39" t="s">
+        <v>490</v>
+      </c>
+      <c r="O39" t="s">
+        <v>491</v>
+      </c>
+      <c r="P39" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>490</v>
+      </c>
+      <c r="R39" t="s">
+        <v>492</v>
+      </c>
+      <c r="S39" t="s">
+        <v>39</v>
+      </c>
+      <c r="T39"/>
+      <c r="U39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V39" t="s">
+        <v>493</v>
+      </c>
+      <c r="W39" t="s">
+        <v>125</v>
+      </c>
+      <c r="X39" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>494</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>495</v>
+      </c>
+      <c r="C40" t="s">
+        <v>496</v>
+      </c>
+      <c r="D40" t="s">
+        <v>497</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
+        <v>498</v>
+      </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>499</v>
+      </c>
+      <c r="I40" t="s">
+        <v>500</v>
+      </c>
+      <c r="J40" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40" t="s">
+        <v>501</v>
+      </c>
+      <c r="L40" t="s">
+        <v>502</v>
+      </c>
+      <c r="M40" t="s">
+        <v>13</v>
+      </c>
+      <c r="N40" t="s">
+        <v>503</v>
+      </c>
+      <c r="O40" t="s">
+        <v>504</v>
+      </c>
+      <c r="P40" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>505</v>
+      </c>
+      <c r="R40" t="s">
+        <v>506</v>
+      </c>
+      <c r="S40" t="s">
+        <v>24</v>
+      </c>
+      <c r="T40" t="s">
+        <v>40</v>
+      </c>
+      <c r="U40" t="s">
+        <v>41</v>
+      </c>
+      <c r="V40" t="s">
+        <v>24</v>
+      </c>
+      <c r="W40" t="s">
+        <v>203</v>
+      </c>
+      <c r="X40" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>507</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>508</v>
+      </c>
+      <c r="C41" t="s">
+        <v>509</v>
+      </c>
+      <c r="D41" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
+        <v>510</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>511</v>
+      </c>
+      <c r="I41" t="s">
+        <v>512</v>
+      </c>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" t="s">
+        <v>513</v>
+      </c>
+      <c r="L41" t="s">
+        <v>514</v>
+      </c>
+      <c r="M41" t="s">
+        <v>15</v>
+      </c>
+      <c r="N41" t="s">
+        <v>515</v>
+      </c>
+      <c r="O41" t="s">
+        <v>516</v>
+      </c>
+      <c r="P41" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>517</v>
+      </c>
+      <c r="R41" t="s">
+        <v>518</v>
+      </c>
+      <c r="S41" t="s">
+        <v>202</v>
+      </c>
+      <c r="T41" t="s">
+        <v>124</v>
+      </c>
+      <c r="U41" t="s">
+        <v>203</v>
+      </c>
+      <c r="V41" t="s">
+        <v>202</v>
+      </c>
+      <c r="W41" t="s">
+        <v>519</v>
+      </c>
+      <c r="X41" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>520</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
